--- a/Data/Data Second Assignment/DataPhase2Rai.xlsx
+++ b/Data/Data Second Assignment/DataPhase2Rai.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uic365-my.sharepoint.com/personal/mrai_uic_edu/Documents/Year 3/Fall 2026/cs 424/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/14270eef50ba1d21/Documents/GitHub/CS424_Fall2016_Project/Data/Data Second Assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{4BDC2F97-0191-4774-9245-2F687FB593C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4BFBF52-3E61-45A6-84E7-82F54134FEFD}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="8_{4BDC2F97-0191-4774-9245-2F687FB593C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9A15691-82FA-4086-A316-403BE2C84EE7}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="2660" windowWidth="28800" windowHeight="15370" xr2:uid="{7226189F-C111-4BD4-AF81-1642F90D934A}"/>
+    <workbookView xWindow="3348" yWindow="3348" windowWidth="17280" windowHeight="8880" xr2:uid="{7226189F-C111-4BD4-AF81-1642F90D934A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="27">
   <si>
     <t>ID</t>
   </si>
@@ -172,7 +172,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -510,24 +510,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26AC3EB7-9977-41F3-895E-43584593A215}">
   <dimension ref="A1:M15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="44.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="44.21875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.36328125" customWidth="1"/>
-    <col min="11" max="11" width="41.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.33203125" customWidth="1"/>
+    <col min="11" max="11" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.21875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -568,7 +568,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -609,7 +609,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B3" s="1">
         <v>46294</v>
       </c>
@@ -634,6 +634,9 @@
       <c r="I3" s="4">
         <v>6.3888888888888884E-2</v>
       </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
       <c r="K3">
         <v>14</v>
       </c>
@@ -644,7 +647,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>46294</v>
       </c>
@@ -669,6 +672,9 @@
       <c r="I4" s="4">
         <v>5.1388888888888887E-2</v>
       </c>
+      <c r="J4" t="s">
+        <v>16</v>
+      </c>
       <c r="K4">
         <v>6</v>
       </c>
@@ -676,7 +682,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>46294</v>
       </c>
@@ -701,6 +707,9 @@
       <c r="I5" s="4">
         <v>5.486111111111111E-2</v>
       </c>
+      <c r="J5" t="s">
+        <v>16</v>
+      </c>
       <c r="K5">
         <v>22</v>
       </c>
@@ -711,7 +720,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>46294</v>
       </c>
@@ -736,6 +745,9 @@
       <c r="I6" s="4">
         <v>5.7638888888888892E-2</v>
       </c>
+      <c r="J6" t="s">
+        <v>16</v>
+      </c>
       <c r="K6">
         <v>16</v>
       </c>
@@ -746,7 +758,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>46294</v>
       </c>
@@ -784,7 +796,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>46294</v>
       </c>
@@ -822,7 +834,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>46294</v>
       </c>
@@ -860,7 +872,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>46294</v>
       </c>
@@ -898,19 +910,19 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" s="1"/>
     </row>
   </sheetData>

--- a/Data/Data Second Assignment/DataPhase2Rai.xlsx
+++ b/Data/Data Second Assignment/DataPhase2Rai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/14270eef50ba1d21/Documents/GitHub/CS424_Fall2016_Project/Data/Data Second Assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{4BDC2F97-0191-4774-9245-2F687FB593C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9A15691-82FA-4086-A316-403BE2C84EE7}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{4BDC2F97-0191-4774-9245-2F687FB593C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82505B78-659A-41E6-A8AB-6913A0557333}"/>
   <bookViews>
     <workbookView xWindow="3348" yWindow="3348" windowWidth="17280" windowHeight="8880" xr2:uid="{7226189F-C111-4BD4-AF81-1642F90D934A}"/>
   </bookViews>
@@ -190,6 +190,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -610,6 +614,9 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
       <c r="B3" s="1">
         <v>46294</v>
       </c>
@@ -648,6 +655,9 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
       <c r="B4" s="1">
         <v>46294</v>
       </c>
@@ -683,6 +693,9 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
       <c r="B5" s="1">
         <v>46294</v>
       </c>
@@ -721,6 +734,9 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
       <c r="B6" s="1">
         <v>46294</v>
       </c>
@@ -759,6 +775,9 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
       <c r="B7" s="1">
         <v>46294</v>
       </c>
@@ -797,6 +816,9 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
       <c r="B8" s="1">
         <v>46294</v>
       </c>
@@ -835,6 +857,9 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
       <c r="B9" s="1">
         <v>46294</v>
       </c>
@@ -873,6 +898,9 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
       <c r="B10" s="1">
         <v>46294</v>
       </c>

--- a/Data/Data Second Assignment/DataPhase2Rai.xlsx
+++ b/Data/Data Second Assignment/DataPhase2Rai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/14270eef50ba1d21/Documents/GitHub/CS424_Fall2016_Project/Data/Data Second Assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="8_{4BDC2F97-0191-4774-9245-2F687FB593C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82505B78-659A-41E6-A8AB-6913A0557333}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="8_{4BDC2F97-0191-4774-9245-2F687FB593C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A15283E4-49A9-4118-881A-1643B8658C33}"/>
   <bookViews>
     <workbookView xWindow="3348" yWindow="3348" windowWidth="17280" windowHeight="8880" xr2:uid="{7226189F-C111-4BD4-AF81-1642F90D934A}"/>
   </bookViews>
@@ -595,10 +595,10 @@
         <v>15</v>
       </c>
       <c r="H2" s="4">
-        <v>4.8611111111111112E-2</v>
+        <v>0.54861111111111116</v>
       </c>
       <c r="I2" s="4">
-        <v>4.8611111111111112E-2</v>
+        <v>0.54861111111111116</v>
       </c>
       <c r="J2" t="s">
         <v>16</v>
@@ -636,10 +636,10 @@
         <v>15</v>
       </c>
       <c r="H3" s="4">
-        <v>6.3194444444444442E-2</v>
+        <v>0.56319444444444444</v>
       </c>
       <c r="I3" s="4">
-        <v>6.3888888888888884E-2</v>
+        <v>0.56388888888888888</v>
       </c>
       <c r="J3">
         <v>12</v>
@@ -677,10 +677,10 @@
         <v>18</v>
       </c>
       <c r="H4" s="4">
-        <v>5.0694444444444445E-2</v>
+        <v>0.55069444444444449</v>
       </c>
       <c r="I4" s="4">
-        <v>5.1388888888888887E-2</v>
+        <v>0.55138888888888893</v>
       </c>
       <c r="J4" t="s">
         <v>16</v>
@@ -715,10 +715,10 @@
         <v>19</v>
       </c>
       <c r="H5" s="4">
-        <v>5.486111111111111E-2</v>
+        <v>0.55486111111111114</v>
       </c>
       <c r="I5" s="4">
-        <v>5.486111111111111E-2</v>
+        <v>0.55486111111111114</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
@@ -756,10 +756,10 @@
         <v>20</v>
       </c>
       <c r="H6" s="4">
-        <v>5.6250000000000001E-2</v>
+        <v>0.55625000000000002</v>
       </c>
       <c r="I6" s="4">
-        <v>5.7638888888888892E-2</v>
+        <v>0.55763888888888891</v>
       </c>
       <c r="J6" t="s">
         <v>16</v>
@@ -797,10 +797,10 @@
         <v>18</v>
       </c>
       <c r="H7" s="4">
-        <v>5.6944444444444443E-2</v>
+        <v>0.55694444444444446</v>
       </c>
       <c r="I7" s="4">
-        <v>5.8333333333333334E-2</v>
+        <v>0.55833333333333335</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -838,10 +838,10 @@
         <v>18</v>
       </c>
       <c r="H8" s="4">
-        <v>6.3194444444444442E-2</v>
+        <v>0.56319444444444444</v>
       </c>
       <c r="I8" s="4">
-        <v>6.5972222222222224E-2</v>
+        <v>0.56597222222222221</v>
       </c>
       <c r="J8">
         <v>11</v>
@@ -879,10 +879,10 @@
         <v>19</v>
       </c>
       <c r="H9" s="4">
-        <v>7.1527777777777773E-2</v>
+        <v>0.57152777777777775</v>
       </c>
       <c r="I9" s="4">
-        <v>7.1527777777777773E-2</v>
+        <v>0.57152777777777775</v>
       </c>
       <c r="J9">
         <v>24</v>
@@ -920,10 +920,10 @@
         <v>18</v>
       </c>
       <c r="H10" s="4">
-        <v>6.9444444444444448E-2</v>
+        <v>0.56944444444444442</v>
       </c>
       <c r="I10" s="4">
-        <v>7.1527777777777773E-2</v>
+        <v>0.57152777777777775</v>
       </c>
       <c r="J10">
         <v>8</v>
